--- a/public/templates/BG_Prime_Inc_Statements.xlsx
+++ b/public/templates/BG_Prime_Inc_Statements.xlsx
@@ -434,6 +434,9 @@
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -482,9 +485,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="5" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="7" fillId="5" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -814,17 +814,17 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="4">
         <v>45988.0</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="5"/>
       <c r="I8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J8" s="5"/>
+      <c r="J8" s="6"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="s">
@@ -836,93 +836,102 @@
       <c r="E9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="4"/>
+      <c r="F9" s="5"/>
       <c r="I9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="4"/>
+      <c r="J9" s="5"/>
     </row>
     <row r="10">
       <c r="I10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="6"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9" t="s">
+      <c r="D12" s="10"/>
+      <c r="E12" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9" t="s">
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14">
+        <f t="shared" ref="J13:J19" si="1">SUM(I13*0.88)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="17"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="21"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="K15" s="22"/>
       <c r="L15" s="22"/>
       <c r="M15" s="22"/>
@@ -941,28 +950,34 @@
       <c r="Z15" s="22"/>
     </row>
     <row r="16">
-      <c r="A16" s="14"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="17"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="21"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="K17" s="22"/>
       <c r="L17" s="22"/>
       <c r="M17" s="22"/>
@@ -981,28 +996,34 @@
       <c r="Z17" s="22"/>
     </row>
     <row r="18">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="17"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="K19" s="22"/>
       <c r="L19" s="22"/>
       <c r="M19" s="22"/>
@@ -1021,22 +1042,22 @@
       <c r="Z19" s="22"/>
     </row>
     <row r="20">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="23"/>
       <c r="G20" s="24" t="s">
         <v>18</v>
       </c>
       <c r="H20" s="24"/>
       <c r="I20" s="25">
-        <f t="shared" ref="I20:J20" si="1">SUM(I13:I19)</f>
+        <f t="shared" ref="I20:J20" si="2">SUM(I13:I19)</f>
         <v>0</v>
       </c>
       <c r="J20" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1069,37 +1090,37 @@
       <c r="Z21" s="22"/>
     </row>
     <row r="22">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9" t="s">
+      <c r="A23" s="9"/>
+      <c r="B23" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9" t="s">
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="11"/>
+      <c r="A24" s="12"/>
       <c r="B24" s="28" t="s">
         <v>22</v>
       </c>
@@ -1109,11 +1130,11 @@
       <c r="F24" s="29"/>
       <c r="G24" s="29"/>
       <c r="H24" s="30"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="14"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="14"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="31" t="s">
         <v>23</v>
       </c>
@@ -1124,7 +1145,7 @@
       <c r="G25" s="32"/>
       <c r="H25" s="33"/>
       <c r="I25" s="34"/>
-      <c r="J25" s="16"/>
+      <c r="J25" s="17"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="35"/>
@@ -1137,11 +1158,11 @@
       <c r="F26" s="32"/>
       <c r="G26" s="32"/>
       <c r="H26" s="33"/>
-      <c r="I26" s="12"/>
+      <c r="I26" s="13"/>
       <c r="J26" s="37"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="14"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="31" t="s">
         <v>25</v>
       </c>
@@ -1152,7 +1173,7 @@
       <c r="G27" s="32"/>
       <c r="H27" s="33"/>
       <c r="I27" s="34"/>
-      <c r="J27" s="16"/>
+      <c r="J27" s="17"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="35"/>
@@ -1165,11 +1186,11 @@
       <c r="F28" s="32"/>
       <c r="G28" s="32"/>
       <c r="H28" s="33"/>
-      <c r="I28" s="12"/>
+      <c r="I28" s="13"/>
       <c r="J28" s="37"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="14"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="31" t="s">
         <v>27</v>
       </c>
@@ -1180,7 +1201,7 @@
       <c r="G29" s="32"/>
       <c r="H29" s="33"/>
       <c r="I29" s="34"/>
-      <c r="J29" s="16"/>
+      <c r="J29" s="17"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="27"/>
@@ -1191,7 +1212,7 @@
       <c r="F30" s="27"/>
       <c r="G30" s="27"/>
       <c r="H30" s="27"/>
-      <c r="I30" s="8" t="s">
+      <c r="I30" s="9" t="s">
         <v>28</v>
       </c>
       <c r="J30" s="40">
@@ -1259,15 +1280,15 @@
       <c r="A33" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="42" t="s">
@@ -1302,26 +1323,26 @@
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
       <c r="I36" s="23" t="s">
         <v>39</v>
       </c>
@@ -1385,14 +1406,14 @@
       <c r="J40" s="51"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
       <c r="I41" s="23" t="s">
         <v>41</v>
       </c>
@@ -1542,15 +1563,15 @@
       <c r="Z46" s="22"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
       <c r="J47" s="52" t="s">
         <v>42</v>
       </c>
@@ -1572,7 +1593,7 @@
     </row>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="C50" s="7"/>
+      <c r="C50" s="8"/>
     </row>
     <row r="51" ht="15.75" customHeight="1"/>
     <row r="52" ht="15.75" customHeight="1"/>
